--- a/docs/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E526D214-5C43-2249-B8E3-77B36E7B9715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8180577-B1F6-6749-8837-5B3C68F65A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="3300" windowWidth="29580" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'2026-05-16 Fat Shallot'!$A$1:$F$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2026-06-21 Chicago Union Rain C'!$A$1:$F$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'2026-06-24 Ridgeville Parks'!$A$1:$F$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2026-09-12 Block Party'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2026-09-12 Block Party'!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="193">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -666,8 +666,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="[m]:ss"/>
-    <numFmt numFmtId="167" formatCode="[hh]:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="[m]:ss"/>
+    <numFmt numFmtId="165" formatCode="[hh]:mm:ss"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1842,22 +1842,22 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1872,7 +1872,7 @@
     <xf numFmtId="46" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1896,7 +1896,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1929,7 +1929,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1950,7 +1950,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1966,13 +1966,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1981,7 +1981,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1993,7 +1993,7 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2001,7 +2001,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2036,7 +2036,7 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2051,7 +2051,7 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2072,7 +2072,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2084,7 +2084,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2093,7 +2093,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2107,7 +2107,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2135,7 +2135,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2175,13 +2175,13 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2284,10 +2284,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5888,7 +5884,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -5898,7 +5894,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>177</v>
       </c>
       <c r="B2" s="145"/>
@@ -6651,7 +6647,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -6661,7 +6657,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>178</v>
       </c>
       <c r="B2" s="145"/>
@@ -7024,7 +7020,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -7034,7 +7030,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>179</v>
       </c>
       <c r="B2" s="145"/>
@@ -7403,7 +7399,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -7413,7 +7409,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>180</v>
       </c>
       <c r="B2" s="145"/>
@@ -8098,7 +8094,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -8108,7 +8104,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>181</v>
       </c>
       <c r="B2" s="145"/>
@@ -8620,7 +8616,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -8630,7 +8626,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>183</v>
       </c>
       <c r="B2" s="145"/>
@@ -9012,7 +9008,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -9022,7 +9018,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>185</v>
       </c>
       <c r="B2" s="145"/>
@@ -9335,7 +9331,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -9345,7 +9341,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="145"/>
@@ -9995,7 +9991,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -10005,7 +10001,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>187</v>
       </c>
       <c r="B2" s="145"/>
@@ -10541,7 +10537,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -10551,7 +10547,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>188</v>
       </c>
       <c r="B2" s="145"/>
@@ -11052,7 +11048,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -11062,7 +11058,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>189</v>
       </c>
       <c r="B2" s="145"/>
@@ -11487,7 +11483,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -11497,7 +11493,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="145"/>
@@ -11816,7 +11812,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -11826,7 +11822,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>191</v>
       </c>
       <c r="B2" s="145"/>
@@ -12110,7 +12106,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3538157-9BE1-8B4C-BB03-B9775E21C6C0}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="8" customWidth="1"/>
@@ -12121,7 +12117,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -12131,7 +12127,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>192</v>
       </c>
       <c r="B2" s="145"/>
@@ -12185,7 +12181,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C5" s="95" t="s">
         <v>2</v>
@@ -12197,7 +12193,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="97">
-        <v>2.2569444444444438E-3</v>
+        <v>2.604166666666667E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12205,7 +12201,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C6" s="95" t="s">
         <v>2</v>
@@ -12214,10 +12210,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="94" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F6" s="97">
-        <v>2.650462962962963E-3</v>
+        <v>2.9513888888888888E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12225,7 +12221,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C7" s="95" t="s">
         <v>2</v>
@@ -12234,10 +12230,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="94" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="97">
-        <v>2.0833333333333329E-3</v>
+        <v>2.8587962962962959E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12245,7 +12241,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C8" s="95" t="s">
         <v>2</v>
@@ -12254,10 +12250,10 @@
         <v>3</v>
       </c>
       <c r="E8" s="94" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F8" s="97">
-        <v>2.0486111111111109E-3</v>
+        <v>2.5810185185185189E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12265,7 +12261,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="C9" s="95" t="s">
         <v>2</v>
@@ -12274,10 +12270,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="94" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F9" s="97">
-        <v>3.414351851851852E-3</v>
+        <v>3.0439814814814808E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12285,7 +12281,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C10" s="95" t="s">
         <v>2</v>
@@ -12297,7 +12293,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="97">
-        <v>2.488425925925926E-3</v>
+        <v>2.604166666666667E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12305,7 +12301,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C11" s="95" t="s">
         <v>2</v>
@@ -12317,7 +12313,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="97">
-        <v>3.5995370370370369E-3</v>
+        <v>2.5810185185185189E-3</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12325,7 +12321,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="C12" s="95" t="s">
         <v>2</v>
@@ -12334,10 +12330,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="94" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F12" s="97">
-        <v>2.0949074074074069E-3</v>
+        <v>3.368055555555556E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12345,19 +12341,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="98" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="96" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="94" t="s">
         <v>35</v>
       </c>
       <c r="F13" s="97">
-        <v>2.5810185185185189E-3</v>
+        <v>2.743055555555555E-3</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12365,7 +12361,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C14" s="95" t="s">
         <v>2</v>
@@ -12374,10 +12370,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" s="97">
-        <v>2.8587962962962959E-3</v>
+        <v>2.650462962962963E-3</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12385,7 +12381,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="C15" s="95" t="s">
         <v>2</v>
@@ -12394,10 +12390,10 @@
         <v>3</v>
       </c>
       <c r="E15" s="94" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F15" s="97">
-        <v>2.430555555555556E-3</v>
+        <v>2.2569444444444438E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12405,7 +12401,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="C16" s="95" t="s">
         <v>2</v>
@@ -12414,10 +12410,10 @@
         <v>3</v>
       </c>
       <c r="E16" s="94" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F16" s="97">
-        <v>3.0439814814814808E-3</v>
+        <v>2.719907407407407E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12425,7 +12421,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="C17" s="95" t="s">
         <v>2</v>
@@ -12437,259 +12433,128 @@
         <v>44</v>
       </c>
       <c r="F17" s="97">
-        <v>3.3217592592592591E-3</v>
+        <v>2.488425925925926E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="149"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="150"/>
+      <c r="A18" s="93">
+        <v>15</v>
+      </c>
+      <c r="B18" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="97">
+        <v>2.0833333333333329E-3</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="93">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="94" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="100" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="101" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="96" t="s">
         <v>3</v>
       </c>
       <c r="E19" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="97">
+        <v>2.0486111111111109E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="93">
+        <v>17</v>
+      </c>
+      <c r="B20" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="97">
+        <v>1.9791666666666668E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="93">
+        <v>18</v>
+      </c>
+      <c r="B21" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="97">
-        <v>2.719907407407407E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="102">
-        <v>16</v>
-      </c>
-      <c r="B20" s="94" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="94" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="97">
-        <v>2.7893518518518519E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="103">
-        <v>17</v>
-      </c>
-      <c r="B21" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="94" t="s">
+      <c r="F21" s="97">
+        <v>3.5995370370370369E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="93">
+        <v>19</v>
+      </c>
+      <c r="B22" s="94" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="97">
-        <v>3.368055555555556E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="93">
-        <v>18</v>
-      </c>
-      <c r="B22" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="94" t="s">
-        <v>35</v>
-      </c>
       <c r="F22" s="97">
-        <v>2.9513888888888888E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="93">
-        <v>19</v>
-      </c>
-      <c r="B23" s="94" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="94" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="97">
-        <v>2.604166666666667E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="93">
-        <v>20</v>
-      </c>
-      <c r="B24" s="94" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="94" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="97">
-        <v>3.2291666666666671E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="93">
-        <v>21</v>
-      </c>
-      <c r="B25" s="94" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="104">
-        <v>2.743055555555555E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="93">
-        <v>22</v>
-      </c>
-      <c r="B26" s="94" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="94" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="97">
-        <v>2.604166666666667E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="93">
-        <v>23</v>
-      </c>
-      <c r="B27" s="94" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="94" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" s="97">
-        <v>1.9791666666666668E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="93">
-        <v>24</v>
-      </c>
-      <c r="B28" s="94" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="97">
-        <v>2.5810185185185189E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="93">
-        <v>25</v>
-      </c>
-      <c r="B29" s="105" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="106" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="107" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="105" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="108">
-        <v>4.6874999999999998E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="54"/>
-      <c r="B30" s="55" t="s">
+        <v>3.3217592592592591E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="54"/>
+      <c r="B23" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56">
-        <f>SUM(F4:F17,F19:F29)</f>
-        <v>6.9317129629629617E-2</v>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="56">
+        <f>SUM(F4:F22)</f>
+        <v>5.0671296296296305E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:F16 B17:F17 A17:A18 A19:F28 A29 A30:F30">
+  <conditionalFormatting sqref="A4:F16 B17:F17 A17:A18 A19:F23">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -12698,56 +12563,44 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{D4232A93-C1CB-E248-9A4A-CC9732E8CC5A}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{367C14C6-23BD-924D-8D2A-A97FBF2CA6A4}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{E05024B1-479B-7E4B-86B6-DCB57DB60E04}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{11C58E40-4FAA-3340-ADAD-A6DD49ECB147}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{F22E6491-6D38-414A-9DE2-ADA972272A0B}"/>
-    <hyperlink ref="D6" r:id="rId6" xr:uid="{2F83DC13-C4AE-454E-B27F-A6AB99BCC0AC}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{6300C841-F1CB-6347-8055-C0ACE013423A}"/>
-    <hyperlink ref="D7" r:id="rId8" xr:uid="{F2953FC0-705C-4C46-85D3-02650FB54DCB}"/>
-    <hyperlink ref="C8" r:id="rId9" xr:uid="{5E343141-D181-5541-9291-A0DE4EEDCD7B}"/>
-    <hyperlink ref="D8" r:id="rId10" xr:uid="{F4FE0848-9CEA-0C43-84D2-097A5AC38AC4}"/>
-    <hyperlink ref="C9" r:id="rId11" xr:uid="{9ED3E6B0-153D-5449-B1A7-F03D18FFB1A6}"/>
-    <hyperlink ref="D9" r:id="rId12" xr:uid="{3FF4B770-45E1-2D4C-9665-79B16857ED03}"/>
-    <hyperlink ref="C10" r:id="rId13" xr:uid="{66A8EBEA-A674-F74B-AAA9-CD654DDBAC35}"/>
-    <hyperlink ref="D10" r:id="rId14" xr:uid="{27C5D37B-7E29-084E-9509-7453C7777577}"/>
-    <hyperlink ref="C11" r:id="rId15" xr:uid="{F750651B-E189-264D-99D9-AF8F8CF487D2}"/>
-    <hyperlink ref="D11" r:id="rId16" xr:uid="{0F8CA7D8-C249-9848-B01D-C0FA9B71224A}"/>
-    <hyperlink ref="C12" r:id="rId17" xr:uid="{17943D1D-F4D9-694F-8B03-5D3BC937FB18}"/>
-    <hyperlink ref="D12" r:id="rId18" xr:uid="{87BD5101-B586-2E49-8252-D6FD75A2D1B5}"/>
-    <hyperlink ref="C13" r:id="rId19" xr:uid="{664D1234-75E5-DF45-A5DD-63447D67192D}"/>
-    <hyperlink ref="D13" r:id="rId20" xr:uid="{6AB414B9-C081-9445-8004-835D846EDDAD}"/>
-    <hyperlink ref="C14" r:id="rId21" xr:uid="{5669780E-3236-0542-B8B4-3DF97B2941D1}"/>
-    <hyperlink ref="D14" r:id="rId22" xr:uid="{3D2AEE5B-98D3-EE4F-AF5A-0AD439AF69A9}"/>
-    <hyperlink ref="C15" r:id="rId23" xr:uid="{CE6C34F9-ADCC-254E-942B-5904E10A1C14}"/>
-    <hyperlink ref="D15" r:id="rId24" xr:uid="{6BDE0C5C-C9FB-4B4F-AC70-9677060F16C6}"/>
-    <hyperlink ref="C16" r:id="rId25" xr:uid="{CA4A2336-B1BD-FB4F-B188-E40769D4572F}"/>
-    <hyperlink ref="D16" r:id="rId26" xr:uid="{67C527E0-8EDE-0B41-AB35-83C8B212ED32}"/>
-    <hyperlink ref="C17" r:id="rId27" xr:uid="{0A73AD83-C7C0-4E4A-96C2-74D1A1C02FD3}"/>
-    <hyperlink ref="D17" r:id="rId28" xr:uid="{707A9F6E-5505-DF4E-98D8-18FC6A55378C}"/>
-    <hyperlink ref="C19" r:id="rId29" xr:uid="{E1BDE48A-4EA0-D74B-8F8B-226F40D048CF}"/>
-    <hyperlink ref="D19" r:id="rId30" xr:uid="{46F45FA3-E1D3-B040-A985-DCCB9E1375BD}"/>
-    <hyperlink ref="C20" r:id="rId31" xr:uid="{E46BC8F9-E1F5-9345-B55F-8F31F84D4E43}"/>
-    <hyperlink ref="D20" r:id="rId32" xr:uid="{60F94FFE-5AC5-0545-8D79-26CA3BEDAE8D}"/>
-    <hyperlink ref="C21" r:id="rId33" xr:uid="{ECCDB158-1990-FF42-B9E8-B11AD8846982}"/>
-    <hyperlink ref="D21" r:id="rId34" xr:uid="{68782832-C14B-D443-ADC0-561BA0BF0C41}"/>
-    <hyperlink ref="C22" r:id="rId35" xr:uid="{E7B06481-F5BB-C94C-ABDC-329015EF3AAE}"/>
-    <hyperlink ref="D22" r:id="rId36" xr:uid="{69C6C633-B046-2440-B836-9CCED1E35573}"/>
-    <hyperlink ref="C23" r:id="rId37" xr:uid="{EB48B85F-7FD3-4741-A29D-024BA7C73AE0}"/>
-    <hyperlink ref="D23" r:id="rId38" xr:uid="{26DD9B48-4D15-1B42-8333-6421B3A9751F}"/>
-    <hyperlink ref="C24" r:id="rId39" xr:uid="{E56534A1-C8C9-414A-A9A2-6B340E90AA30}"/>
-    <hyperlink ref="D24" r:id="rId40" xr:uid="{18342DD5-1521-3F4B-A6F0-617737D15237}"/>
-    <hyperlink ref="C25" r:id="rId41" xr:uid="{F2B0D3C6-4566-6E4A-AC2F-7270E3E6E2E2}"/>
-    <hyperlink ref="D25" r:id="rId42" xr:uid="{63196EC7-A944-734B-8956-8D5B23C8C360}"/>
-    <hyperlink ref="C26" r:id="rId43" xr:uid="{B6EFDDD9-283D-324A-9872-C2BF7AB68327}"/>
-    <hyperlink ref="D26" r:id="rId44" xr:uid="{98FF9618-4D73-0C45-9D98-3919EF234F80}"/>
-    <hyperlink ref="C27" r:id="rId45" xr:uid="{957AAE86-B641-5A4A-A9DC-F95FA55B0F89}"/>
-    <hyperlink ref="D27" r:id="rId46" xr:uid="{AA3142A0-A994-4449-8BDA-3E3824B9B478}"/>
-    <hyperlink ref="C28" r:id="rId47" xr:uid="{E0DC05D0-D6E3-194E-8ACD-684829F0229C}"/>
-    <hyperlink ref="D28" r:id="rId48" xr:uid="{244E6D6E-C10E-064C-A1A5-85F9D64A374D}"/>
-    <hyperlink ref="C29" r:id="rId49" xr:uid="{C4DD953A-C9F2-1A4C-BD04-088981DF276F}"/>
-    <hyperlink ref="D29" r:id="rId50" xr:uid="{2504B531-DA57-F441-9001-4C7B50BECE16}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{D9DA177A-189A-764F-AFCB-1C77FF359938}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{B65AF94C-287F-9547-9FE9-3FFEF8C65603}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{4B0FE00E-A9DE-CE47-9EBB-E130E69A3FE2}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{2B957138-8603-FF40-8870-89A7EB0577C9}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{B175B4B5-732E-9542-87E6-8B2B21313B3C}"/>
+    <hyperlink ref="D6" r:id="rId6" xr:uid="{D864685C-0ACC-0C47-AFF3-377E6B809713}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{8E1D8681-BB8B-D542-B311-1401144027B2}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{82B90030-FC95-6442-81A2-38612AD1AFFE}"/>
+    <hyperlink ref="C8" r:id="rId9" xr:uid="{439FDFB7-7399-A244-B5F9-0F59793B34F7}"/>
+    <hyperlink ref="D8" r:id="rId10" xr:uid="{5349162C-0619-8243-B830-5EE11C9B23E6}"/>
+    <hyperlink ref="C9" r:id="rId11" xr:uid="{A8A9EF22-AF54-1440-B6C6-BA2876458184}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{9DFACCDA-8546-BA46-BAEC-D932F7BB046A}"/>
+    <hyperlink ref="C10" r:id="rId13" xr:uid="{915736C2-8B13-D14E-8998-49951DEEE0DC}"/>
+    <hyperlink ref="D10" r:id="rId14" xr:uid="{F82E15F1-5A03-214F-B92E-DC89287213EE}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{34BFD844-9AFE-BF43-83B4-65322B3EEABC}"/>
+    <hyperlink ref="D11" r:id="rId16" xr:uid="{16F54A55-64C5-1A46-B26E-C502ECCB92B5}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{156A48EB-B4F4-CC45-BF6A-16C60789F779}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{3935FEB1-0A60-0C4F-8A2E-6AE387A5DE58}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{2E32667E-DDFE-D149-B06B-80DC85010508}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{5F5C4F7E-94DE-8F4B-A5E3-7C6CEB469B32}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{D2A1D70D-36E6-8F4F-BD12-4199AFD24044}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{4E1072B6-D821-E746-B1AF-DC7CD670644D}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{C228F52B-53CF-1448-AE5C-BEF5F54147CF}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{353FEEBC-B4A0-114F-9396-41FB99774617}"/>
+    <hyperlink ref="C16" r:id="rId25" xr:uid="{59577456-5FF5-9D43-B85C-837735DEC7B4}"/>
+    <hyperlink ref="D16" r:id="rId26" xr:uid="{42AAB2A3-0AF5-A248-9EC4-7A35205FAA74}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{382790BD-7A61-5A41-A944-097DB1CF8F0E}"/>
+    <hyperlink ref="D17" r:id="rId28" xr:uid="{9B4A7551-C5C8-3541-8FA8-D94AF0E8F4BD}"/>
+    <hyperlink ref="C18" r:id="rId29" xr:uid="{8C454EA2-8194-1240-8E32-B1C97DA3AD27}"/>
+    <hyperlink ref="D18" r:id="rId30" xr:uid="{518FBAFF-AB52-CC43-816D-3129AEA862E9}"/>
+    <hyperlink ref="C19" r:id="rId31" xr:uid="{C0EAFD09-AEFB-7047-AED4-747A78793BA4}"/>
+    <hyperlink ref="D19" r:id="rId32" xr:uid="{8CDF8C3A-654C-594E-BE43-EFE4448F9D7A}"/>
+    <hyperlink ref="C20" r:id="rId33" xr:uid="{6219A849-C629-5943-B638-B8B93C15F74E}"/>
+    <hyperlink ref="D20" r:id="rId34" xr:uid="{01F97FC7-00BE-4F45-A275-CD9874F0B4AE}"/>
+    <hyperlink ref="C21" r:id="rId35" xr:uid="{E9936282-51F5-4843-9B88-BF0F2F66F3F9}"/>
+    <hyperlink ref="D21" r:id="rId36" xr:uid="{E88DA8D9-0CD4-E54D-B450-3EA5CE4D3247}"/>
+    <hyperlink ref="C22" r:id="rId37" xr:uid="{3D51BFC1-9D02-9C46-BF29-E1C610AAEB0E}"/>
+    <hyperlink ref="D22" r:id="rId38" xr:uid="{C10DC23A-1AA3-2A4D-A8FC-2DBB0258CD38}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -12767,7 +12620,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -12777,7 +12630,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>166</v>
       </c>
       <c r="B2" s="145"/>
@@ -14950,7 +14803,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -14960,7 +14813,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>174</v>
       </c>
       <c r="B2" s="145"/>
@@ -15396,7 +15249,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="144" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="145"/>
@@ -15406,7 +15259,7 @@
       <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="147" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="145"/>

--- a/docs/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40D203-2AA1-724A-8892-E5646617275A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062BAFB5-F205-FE4A-85D7-A525E03BD3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="3280" windowWidth="29580" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6480" yWindow="600" windowWidth="24020" windowHeight="19600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="190">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -825,7 +825,7 @@
       <b/>
       <u/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Courier New"/>
       <family val="1"/>
     </font>
@@ -862,7 +862,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="79">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -1864,6 +1864,17 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1874,13 +1885,100 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
@@ -1891,7 +1989,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2264,6 +2362,37 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2307,80 +2436,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="19" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="17" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2965,10 +3056,10 @@
       <c r="A4" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="182" t="s">
+      <c r="B4" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="121" t="s">
@@ -3022,10 +3113,10 @@
       <c r="A5" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="182" t="s">
+      <c r="B5" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="114" t="s">
@@ -3079,10 +3170,10 @@
       <c r="A6" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="182" t="s">
+      <c r="B6" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="109" t="s">
@@ -3152,10 +3243,10 @@
       <c r="A7" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="182" t="s">
+      <c r="B7" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="114" t="s">
@@ -3215,10 +3306,10 @@
       <c r="A8" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="182" t="s">
+      <c r="B8" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="109" t="s">
@@ -3278,10 +3369,10 @@
       <c r="A9" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="182" t="s">
+      <c r="B9" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="114" t="s">
@@ -3351,10 +3442,10 @@
       <c r="A10" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="182" t="s">
+      <c r="B10" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="109" t="s">
@@ -3440,10 +3531,10 @@
       <c r="A11" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="182" t="s">
+      <c r="B11" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="114" t="s">
@@ -3495,10 +3586,10 @@
       <c r="A12" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="182" t="s">
+      <c r="B12" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="109" t="s">
@@ -3564,10 +3655,10 @@
       <c r="A13" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="182" t="s">
+      <c r="B13" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="114" t="s">
@@ -3631,10 +3722,10 @@
       <c r="A14" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="182" t="s">
+      <c r="B14" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="109" t="s">
@@ -3688,10 +3779,10 @@
       <c r="A15" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="182" t="s">
+      <c r="B15" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="114" t="s">
@@ -3741,10 +3832,10 @@
       <c r="A16" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="182" t="s">
+      <c r="B16" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="109" t="s">
@@ -3820,10 +3911,10 @@
       <c r="A17" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="182" t="s">
+      <c r="B17" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="114" t="s">
@@ -3891,10 +3982,10 @@
       <c r="A18" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="182" t="s">
+      <c r="B18" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="109" t="s">
@@ -3946,10 +4037,10 @@
       <c r="A19" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="182" t="s">
+      <c r="B19" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="114" t="s">
@@ -4015,10 +4106,10 @@
       <c r="A20" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="182" t="s">
+      <c r="B20" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="109" t="s">
@@ -4080,10 +4171,10 @@
       <c r="A21" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="182" t="s">
+      <c r="B21" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="114" t="s">
@@ -4151,10 +4242,10 @@
       <c r="A22" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="182" t="s">
+      <c r="B22" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="109" t="s">
@@ -4204,10 +4295,10 @@
       <c r="A23" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="182" t="s">
+      <c r="B23" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="114" t="s">
@@ -4291,10 +4382,10 @@
       <c r="A24" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="182" t="s">
+      <c r="B24" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="109" t="s">
@@ -4360,7 +4451,7 @@
       <c r="A25" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="182" t="s">
+      <c r="B25" s="141" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="119"/>
@@ -4427,10 +4518,10 @@
       <c r="A26" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="182" t="s">
+      <c r="B26" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="109" t="s">
@@ -4504,10 +4595,10 @@
       <c r="A27" s="114" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="182" t="s">
+      <c r="B27" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="114" t="s">
@@ -4561,10 +4652,10 @@
       <c r="A28" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="182" t="s">
+      <c r="B28" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="109" t="s">
@@ -4622,10 +4713,10 @@
       <c r="A29" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="182" t="s">
+      <c r="B29" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="114" t="s">
@@ -4687,10 +4778,10 @@
       <c r="A30" s="109" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="182" t="s">
+      <c r="B30" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="109" t="s">
@@ -4766,10 +4857,10 @@
       <c r="A31" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="182" t="s">
+      <c r="B31" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="114" t="s">
@@ -4851,10 +4942,10 @@
       <c r="A32" s="109" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="182" t="s">
+      <c r="B32" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="109" t="s">
@@ -4908,10 +4999,10 @@
       <c r="A33" s="114" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="182" t="s">
+      <c r="B33" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="114" t="s">
@@ -4975,10 +5066,10 @@
       <c r="A34" s="109" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="182" t="s">
+      <c r="B34" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="109" t="s">
@@ -5054,10 +5145,10 @@
       <c r="A35" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="182" t="s">
+      <c r="B35" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="114" t="s">
@@ -5121,10 +5212,10 @@
       <c r="A36" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="B36" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="182" t="s">
+      <c r="B36" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="109" t="s">
@@ -5192,10 +5283,10 @@
       <c r="A37" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="182" t="s">
+      <c r="B37" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="114" t="s">
@@ -5251,10 +5342,10 @@
       <c r="A38" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="182" t="s">
+      <c r="B38" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="109" t="s">
@@ -5324,10 +5415,10 @@
       <c r="A39" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="182" t="s">
+      <c r="B39" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="114" t="s">
@@ -5389,10 +5480,10 @@
       <c r="A40" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="182" t="s">
+      <c r="B40" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="109" t="s">
@@ -5444,10 +5535,10 @@
       <c r="A41" s="114" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="182" t="s">
+      <c r="B41" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="114" t="s">
@@ -5497,10 +5588,10 @@
       <c r="A42" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="182" t="s">
+      <c r="B42" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="109" t="s">
@@ -5556,10 +5647,10 @@
       <c r="A43" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="182" t="s">
+      <c r="B43" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="114" t="s">
@@ -5623,10 +5714,10 @@
       <c r="A44" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="182" t="s">
+      <c r="B44" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="109" t="s">
@@ -5678,10 +5769,10 @@
       <c r="A45" s="114" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="182" t="s">
+      <c r="B45" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="114" t="s">
@@ -5743,10 +5834,10 @@
       <c r="A46" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="182" t="s">
+      <c r="B46" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="109" t="s">
@@ -5796,10 +5887,10 @@
       <c r="A47" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="B47" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="182" t="s">
+      <c r="B47" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="114" t="s">
@@ -5932,10 +6023,10 @@
       <c r="A49" s="114" t="s">
         <v>133</v>
       </c>
-      <c r="B49" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="182" t="s">
+      <c r="B49" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="141" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="114" t="s">
@@ -6164,24 +6255,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -6469,24 +6560,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -7053,7 +7144,7 @@
       <c r="B31" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="183" t="s">
+      <c r="C31" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="17" t="s">
@@ -7235,24 +7326,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -7608,24 +7699,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -7734,10 +7825,10 @@
       <c r="B8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="183" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="183" t="s">
+      <c r="C8" s="142" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="142" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="10" t="s">
@@ -7835,7 +7926,7 @@
       <c r="B13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="183" t="s">
+      <c r="C13" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="17" t="s">
@@ -7996,24 +8087,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -8183,10 +8274,10 @@
       <c r="B11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="183" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="183" t="s">
+      <c r="C11" s="142" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="142" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="10" t="s">
@@ -8365,7 +8456,7 @@
       <c r="B20" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="183" t="s">
+      <c r="C20" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="17" t="s">
@@ -8700,24 +8791,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -8988,7 +9079,7 @@
       <c r="B16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="183" t="s">
+      <c r="C16" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="17" t="s">
@@ -9225,24 +9316,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -9412,7 +9503,7 @@
       <c r="B11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="183" t="s">
+      <c r="C11" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="17" t="s">
@@ -9620,24 +9711,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -9825,7 +9916,7 @@
       <c r="B12" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="183" t="s">
+      <c r="C12" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="17" t="s">
@@ -9946,24 +10037,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -10274,7 +10365,7 @@
       <c r="B18" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="183" t="s">
+      <c r="C18" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="17" t="s">
@@ -10609,24 +10700,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -10896,7 +10987,7 @@
       <c r="B16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="183" t="s">
+      <c r="C16" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="17" t="s">
@@ -11341,24 +11432,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -11669,24 +11760,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -12104,24 +12195,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -12433,24 +12524,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -12601,7 +12692,7 @@
       <c r="B10" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="142" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="17" t="s">
@@ -12744,40 +12835,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="143" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="163"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="146" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="166"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="148"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="167"/>
-      <c r="B3" s="168" t="s">
+      <c r="A3" s="138"/>
+      <c r="B3" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="169" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="169" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="168" t="s">
+      <c r="C3" s="183" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="183" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="170" t="s">
+      <c r="F3" s="140" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12785,768 +12876,435 @@
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="179" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="C4" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="181" t="s">
         <v>43</v>
       </c>
       <c r="F4" s="24">
-        <v>2.604166666666667E-3</v>
+        <v>2.60416666666667E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="179" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="C5" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="181" t="s">
         <v>34</v>
       </c>
       <c r="F5" s="24">
-        <v>2.5810185185185189E-3</v>
+        <v>2.5810185185185198E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
+      <c r="B6" s="179" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="181" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="24">
-        <v>3.368055555555556E-3</v>
+        <v>2.7893518518518502E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>34</v>
+      <c r="B7" s="179" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="181" t="s">
+        <v>43</v>
       </c>
       <c r="F7" s="24">
-        <v>2.743055555555555E-3</v>
+        <v>2.2569444444444399E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>39</v>
+      <c r="B8" s="179" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="181" t="s">
+        <v>34</v>
       </c>
       <c r="F8" s="24">
-        <v>2.0949074074074069E-3</v>
+        <v>2.7430555555555602E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>6</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>43</v>
+      <c r="B9" s="179" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="181" t="s">
+        <v>54</v>
       </c>
       <c r="F9" s="24">
-        <v>2.488425925925926E-3</v>
+        <v>1.9791666666666699E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>54</v>
+      <c r="B10" s="179" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="181" t="s">
+        <v>43</v>
       </c>
       <c r="F10" s="24">
-        <v>1.9791666666666668E-3</v>
+        <v>2.04861111111111E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>8</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="B11" s="179" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="181" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="24">
-        <v>2.5810185185185189E-3</v>
+        <v>2.9513888888888901E-3</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>9</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>54</v>
+      <c r="B12" s="179" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="181" t="s">
+        <v>39</v>
       </c>
       <c r="F12" s="24">
-        <v>3.0439814814814808E-3</v>
+        <v>2.4305555555555599E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>10</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="B13" s="179" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="181" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="24">
-        <v>2.9513888888888888E-3</v>
+        <v>2.71990740740741E-3</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="B14" s="179" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="181" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="24">
-        <v>2.430555555555556E-3</v>
+        <v>2.6504629629629599E-3</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>12</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>39</v>
+      <c r="B15" s="179" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="181" t="s">
+        <v>43</v>
       </c>
       <c r="F15" s="24">
-        <v>3.414351851851852E-3</v>
+        <v>2.60416666666667E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>43</v>
+      <c r="B16" s="179" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="178" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="178" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>54</v>
       </c>
       <c r="F16" s="24">
-        <v>2.2569444444444438E-3</v>
+        <f>'Song Tracker'!F28</f>
+        <v>3.0439814814814808E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>14</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="B17" s="179" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="181" t="s">
         <v>39</v>
       </c>
       <c r="F17" s="24">
-        <v>2.7893518518518519E-3</v>
+        <v>2.0833333333333298E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>15</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>34</v>
+      <c r="B18" s="179" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="181" t="s">
+        <v>43</v>
       </c>
       <c r="F18" s="24">
-        <v>3.5995370370370369E-3</v>
+        <v>2.8587962962962998E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>16</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="B19" s="179" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="181" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="24">
+        <v>3.59953703703704E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="172">
+        <v>17</v>
+      </c>
+      <c r="B20" s="180" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="182" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="173">
+        <v>3.2291666666666701E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>18</v>
+      </c>
+      <c r="B21" s="179" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="24">
-        <v>2.0486111111111109E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
-        <v>17</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="24">
-        <v>3.3217592592592591E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="172"/>
-      <c r="B21" s="173" t="s">
+      <c r="F21" s="24">
+        <v>3.32175925925926E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="174"/>
+      <c r="B22" s="175" t="s">
         <v>165</v>
       </c>
-      <c r="C21" s="174"/>
-      <c r="D21" s="174"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="175">
-        <f>SUM(F4:F20)</f>
-        <v>4.6296296296296294E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="177" t="s">
-        <v>167</v>
-      </c>
-      <c r="B22" s="176"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="184"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="185"/>
       <c r="E22" s="176"/>
-      <c r="F22" s="178"/>
-    </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="179">
-        <v>1</v>
-      </c>
-      <c r="B23" s="180" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="186" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="186" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="180" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="181">
-        <v>2.1875000000000002E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
-        <v>2</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="24">
-        <v>2.719907407407407E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
-        <v>3</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="24">
-        <v>2.650462962962963E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
-        <v>4</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="24">
-        <v>1.747685185185185E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
-        <v>5</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="24">
-        <v>3.472222222222222E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
-        <v>6</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="185"/>
-      <c r="E28" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="24">
-        <v>3.8541666666666672E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
-        <v>7</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="24">
-        <v>4.1319444444444442E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
-        <v>8</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="24">
-        <v>2.604166666666667E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
-        <v>9</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="24">
-        <v>2.8587962962962959E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
-        <v>10</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" s="24">
-        <v>2.604166666666667E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
-        <v>11</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="24">
-        <v>4.6874999999999998E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
-        <v>12</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34" s="24">
-        <v>3.2291666666666671E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
-        <v>13</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="24">
-        <v>2.0833333333333329E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
-        <v>14</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="24">
-        <v>1.93287037037037E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
-        <v>15</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C37" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="24">
-        <v>3.460648148148148E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
-        <v>16</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" s="24">
-        <v>5.9606481481481481E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" s="171"/>
-      <c r="D39" s="171"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="16">
-        <f>SUM(F23:F38)</f>
-        <v>5.018518518518518E-2</v>
-      </c>
-    </row>
+      <c r="F22" s="177">
+        <f>SUM(F4:F21)</f>
+        <v>4.8495370370370397E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{888BB888-9C01-214B-A5AE-4896A3E9EFE0}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{07BBBCAB-9BA0-4D4D-869B-05D415CA1D47}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{4F330995-AB83-DC46-B1D0-A31052E5DF11}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{50BEB03C-7E47-934E-956A-1649A782B6F3}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{2AFC4953-D86A-F64A-A4FF-5711C9B4C68F}"/>
-    <hyperlink ref="D6" r:id="rId6" xr:uid="{4D7DE131-7C87-E645-84AD-74EF64907BB3}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{CDD4D1FE-A988-7849-A40B-7E0C217A2CF6}"/>
-    <hyperlink ref="D7" r:id="rId8" xr:uid="{D79C1C69-B145-754D-99EF-0520249FB070}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{CF57F841-A802-A54F-925D-5F50A0112068}"/>
-    <hyperlink ref="D9" r:id="rId10" xr:uid="{EC6E4D9C-99D8-3F47-9925-6DB8D62D6714}"/>
-    <hyperlink ref="C10" r:id="rId11" xr:uid="{6B733EC6-62BE-4448-BC0F-457F3748BD87}"/>
-    <hyperlink ref="D10" r:id="rId12" xr:uid="{6CD24F54-A7F7-104F-9D64-71054B4F07AC}"/>
-    <hyperlink ref="C11" r:id="rId13" xr:uid="{C285C1ED-1BF8-3942-8B5D-5452B4EE13BE}"/>
-    <hyperlink ref="D11" r:id="rId14" xr:uid="{966FC5A9-9C99-CB44-B59A-2D808A2C0826}"/>
-    <hyperlink ref="C12" r:id="rId15" xr:uid="{F18D352B-8585-4F4D-BC99-D7DE2C69564E}"/>
-    <hyperlink ref="D12" r:id="rId16" xr:uid="{088AEA7F-A2A8-B34E-983D-C484E4550971}"/>
-    <hyperlink ref="C13" r:id="rId17" xr:uid="{65F3601F-0AEB-E04B-BC90-488C34F7D7D3}"/>
-    <hyperlink ref="D13" r:id="rId18" xr:uid="{1B8D60F8-D6E2-D143-B15C-B4BC907A2FA3}"/>
-    <hyperlink ref="C14" r:id="rId19" xr:uid="{DF4DC6ED-D166-374F-AFC6-882159C73FF6}"/>
-    <hyperlink ref="D14" r:id="rId20" xr:uid="{AA37FD01-BCFB-8442-98FD-033153A65436}"/>
-    <hyperlink ref="C15" r:id="rId21" xr:uid="{E91C4C74-82A1-154A-9AB5-DAB48609E41D}"/>
-    <hyperlink ref="D15" r:id="rId22" xr:uid="{64170794-984D-0844-A78A-91ABB4160BD7}"/>
-    <hyperlink ref="C16" r:id="rId23" xr:uid="{F29E49FB-A4BD-DD41-B114-2FA7E4DBB5CE}"/>
-    <hyperlink ref="D16" r:id="rId24" xr:uid="{7822EECA-D4BF-944C-886C-46EB2F04B1E3}"/>
-    <hyperlink ref="C17" r:id="rId25" xr:uid="{964E53D6-E3E9-A941-AB39-DB0E307BBD37}"/>
-    <hyperlink ref="D17" r:id="rId26" xr:uid="{B82B4BEE-69C1-1347-B095-8277872DE1DB}"/>
-    <hyperlink ref="C18" r:id="rId27" xr:uid="{0713467B-189E-ED44-AC43-167C4549723E}"/>
-    <hyperlink ref="D18" r:id="rId28" xr:uid="{E0DFF2A1-F2DC-9044-ABC0-4B40EAE252BF}"/>
-    <hyperlink ref="C19" r:id="rId29" xr:uid="{99936BB7-4414-A642-80B4-26351F122601}"/>
-    <hyperlink ref="D19" r:id="rId30" xr:uid="{6BB3CF91-2008-D147-9FA5-8840E536EC00}"/>
-    <hyperlink ref="C23" r:id="rId31" xr:uid="{D3F77900-BC81-5A40-9326-F6722B5C052E}"/>
-    <hyperlink ref="D23" r:id="rId32" xr:uid="{11EC5856-F91B-A44C-B85F-7CA004D30532}"/>
-    <hyperlink ref="C24" r:id="rId33" xr:uid="{7163151E-F861-4942-A8BE-D4680AA424F2}"/>
-    <hyperlink ref="D24" r:id="rId34" xr:uid="{8FB461BB-8F2B-A448-A1E7-7DBCE0E4CE14}"/>
-    <hyperlink ref="C25" r:id="rId35" xr:uid="{59C69372-2A35-E941-B866-19BB3164A413}"/>
-    <hyperlink ref="D25" r:id="rId36" xr:uid="{1CB8366A-3448-5549-821B-674CCBF3247C}"/>
-    <hyperlink ref="C26" r:id="rId37" xr:uid="{F9305938-A290-C94C-A24F-3F9E4A4BA25B}"/>
-    <hyperlink ref="D26" r:id="rId38" xr:uid="{5A7EFB42-7524-1942-B691-A7BF56FD9198}"/>
-    <hyperlink ref="C27" r:id="rId39" xr:uid="{0FBC77BA-49FD-C445-9173-8EC54518D4EE}"/>
-    <hyperlink ref="D27" r:id="rId40" xr:uid="{F594ADB2-D9A6-4842-9094-5D36F284E709}"/>
-    <hyperlink ref="C28" r:id="rId41" xr:uid="{16883EFF-C10C-D746-B402-87F4252BBF3B}"/>
-    <hyperlink ref="C29" r:id="rId42" xr:uid="{F2715B97-C25B-5F46-B9C5-408923B8ECD9}"/>
-    <hyperlink ref="D29" r:id="rId43" xr:uid="{991EF830-C732-7F43-B92E-CEE95DE81657}"/>
-    <hyperlink ref="C30" r:id="rId44" xr:uid="{FE0ECC30-4D10-3348-A5E0-226BDD51C247}"/>
-    <hyperlink ref="C31" r:id="rId45" xr:uid="{98371BF7-63A9-BF4F-BAFB-0AF4E1831F30}"/>
-    <hyperlink ref="D31" r:id="rId46" xr:uid="{DEFA2F95-67C5-FA47-B01C-3001F5CCC1E5}"/>
-    <hyperlink ref="C32" r:id="rId47" xr:uid="{1BE594A7-5B5D-3A42-BF24-C933873D80B0}"/>
-    <hyperlink ref="D32" r:id="rId48" xr:uid="{AAD9D842-FA9A-2C47-8A03-642DE2861F43}"/>
-    <hyperlink ref="C33" r:id="rId49" xr:uid="{63CC0DAD-1BC5-734C-9C51-1B276815ED09}"/>
-    <hyperlink ref="D33" r:id="rId50" xr:uid="{D019BC56-E89C-DE47-BCEC-E725477445A3}"/>
-    <hyperlink ref="C34" r:id="rId51" xr:uid="{0665497D-17D1-4445-BF2A-3CDDBD4A9A2A}"/>
-    <hyperlink ref="D34" r:id="rId52" xr:uid="{7B3A4D9B-E355-6A40-AE22-EEF6D6520E1F}"/>
-    <hyperlink ref="C35" r:id="rId53" xr:uid="{17EBD69E-C73D-D94C-A2BC-D77E89399C61}"/>
-    <hyperlink ref="D35" r:id="rId54" xr:uid="{6EE7A8DB-68FE-6645-B78F-BFD8B537E468}"/>
-    <hyperlink ref="C36" r:id="rId55" xr:uid="{16B9531E-43EB-5B40-9522-8B15075B01B1}"/>
-    <hyperlink ref="D36" r:id="rId56" xr:uid="{6E1FE125-45DC-5E4B-8B68-7F1FAEC1BC0B}"/>
-    <hyperlink ref="C37" r:id="rId57" xr:uid="{9219CDCA-0B5E-4545-AC44-EB54D13EF508}"/>
-    <hyperlink ref="D37" r:id="rId58" xr:uid="{F36EB773-2A17-B64B-BA7A-92BD6AC81D2C}"/>
-    <hyperlink ref="C38" r:id="rId59" xr:uid="{81F1AFF2-84AA-8D44-BA26-82F90C776791}"/>
-    <hyperlink ref="D38" r:id="rId60" xr:uid="{BF685E86-162F-564E-9F28-0EE59A014709}"/>
-    <hyperlink ref="C8" r:id="rId61" xr:uid="{2918197D-037B-0A4A-86A2-E9F0411EEC8E}"/>
-    <hyperlink ref="D8" r:id="rId62" xr:uid="{A6566426-10E2-5846-849A-491FE9529A50}"/>
-    <hyperlink ref="C20" r:id="rId63" xr:uid="{7388EC25-1C92-084B-96E1-FD110DDEA930}"/>
-    <hyperlink ref="D20" r:id="rId64" xr:uid="{DE9CC48A-ED0A-0E4E-9E30-C7FF298F6726}"/>
-    <hyperlink ref="D30" r:id="rId65" xr:uid="{B30B7792-4916-A84C-BF4C-DCA12DB3AF55}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{0CD0CEF0-CEB2-A246-AC49-3CAC425C85B8}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{1E727846-5FB7-F942-B6E1-4061453D063E}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{DA3C922F-6C54-0142-BCD2-3F7B7760929C}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{C365DACB-9A78-6B41-90A7-FD4D2480B337}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{21930CF6-61E8-E948-A127-589B4EBC3368}"/>
+    <hyperlink ref="D6" r:id="rId6" xr:uid="{9DC59632-AF22-714F-BAC4-6C5E45CC6FAA}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{FA6A5E28-1CAF-5741-95AC-2CDB54CB7642}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{521CCC89-A496-0C4D-95C2-C7B4743FAF4E}"/>
+    <hyperlink ref="C8" r:id="rId9" xr:uid="{641E1802-EA28-8741-95E4-905554D891C3}"/>
+    <hyperlink ref="D8" r:id="rId10" xr:uid="{429C7CDB-A616-1F4A-AC21-B6347D046CE0}"/>
+    <hyperlink ref="C9" r:id="rId11" xr:uid="{9C117EC0-FCCC-2740-A303-C09507421392}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{F9096CAD-F0F2-B243-AAC1-F47C7BB02D28}"/>
+    <hyperlink ref="C10" r:id="rId13" xr:uid="{692E011F-2691-1044-B7C1-B91D93F17C66}"/>
+    <hyperlink ref="D10" r:id="rId14" xr:uid="{9D97B550-A21C-0B4C-96B5-409599034AED}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{55EC590C-1B72-044C-8456-20423FBA8ADA}"/>
+    <hyperlink ref="D11" r:id="rId16" xr:uid="{95D59F58-1983-BA45-9968-C0927799F552}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{33BF72F0-61F0-CF46-9933-47729DDC9702}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{A74E614C-625C-CF45-A94C-82E326E2522A}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{9ED99007-BC44-3441-8E74-C31250DA365F}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{07C87020-817F-5040-806B-7660DC71AE85}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{5F3E4947-3379-5D4B-8AD8-C7C8ABCD61B5}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{B49DA0D5-0856-8B49-B6C2-FCB712E69D8B}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{DC9AAF63-B84B-7C44-960A-D0230BACFA53}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{E9440E9B-D597-E54A-A551-4C8A7FB43178}"/>
+    <hyperlink ref="C17" r:id="rId25" xr:uid="{B932668A-6A89-734A-B68D-28094B1BD55F}"/>
+    <hyperlink ref="D17" r:id="rId26" xr:uid="{09690B73-8AE0-D34B-A684-ADD2C83B26B8}"/>
+    <hyperlink ref="C18" r:id="rId27" xr:uid="{C8E54C2B-AF17-3248-8356-DE741DE479E9}"/>
+    <hyperlink ref="D18" r:id="rId28" xr:uid="{2BE56037-38B3-3B47-9865-C68641F54377}"/>
+    <hyperlink ref="C19" r:id="rId29" xr:uid="{3005EC63-4DA5-C34B-A198-6E5596B25088}"/>
+    <hyperlink ref="D19" r:id="rId30" xr:uid="{4FDBD01C-17A4-C94A-B53A-7281371DDA02}"/>
+    <hyperlink ref="C20" r:id="rId31" xr:uid="{B91EBDC5-ABC4-914D-B066-5F3F1A7A2AF8}"/>
+    <hyperlink ref="D20" r:id="rId32" xr:uid="{3FA66CC4-2C42-0C4D-869E-1C4EDECE3172}"/>
+    <hyperlink ref="C21" r:id="rId33" xr:uid="{82814134-668A-204E-A94A-41E70CCC41B7}"/>
+    <hyperlink ref="D21" r:id="rId34" xr:uid="{1F3E435F-9F35-0140-A080-6722111D443E}"/>
+    <hyperlink ref="C16" r:id="rId35" xr:uid="{82AC4A7B-646F-B949-81E6-4FC846671668}"/>
+    <hyperlink ref="D16" r:id="rId36" xr:uid="{8B381F23-5675-894E-ACE2-ACD58A2CD001}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="79" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13566,24 +13324,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="82" t="s">
@@ -14069,24 +13827,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="82" t="s">
@@ -14389,14 +14147,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="142" t="s">
+      <c r="A18" s="153" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="143"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="144"/>
+      <c r="B18" s="154"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="155"/>
     </row>
     <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="93">
@@ -14737,24 +14495,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="159" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="150"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="161"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="156" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="158"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
@@ -15093,12 +14851,12 @@
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="61"/>
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
+      <c r="C19" s="160"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="160"/>
       <c r="F19" s="75">
         <f>SUM(F4:F18)</f>
         <v>4.0509259259259259E-2</v>
@@ -15160,14 +14918,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="163" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="153"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="164"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
@@ -15470,14 +15228,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="154" t="s">
+      <c r="A17" s="165" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="144"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+      <c r="F17" s="155"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="43">
@@ -15817,24 +15575,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="160"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="171"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="166" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="157"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="168"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="86" t="s">
@@ -16252,24 +16010,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="149" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">

--- a/docs/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062BAFB5-F205-FE4A-85D7-A525E03BD3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AC38BD-B75F-0645-8B3A-59F2C2ED86BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6480" yWindow="600" windowWidth="24020" windowHeight="19600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6480" yWindow="600" windowWidth="24020" windowHeight="19600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'2026-06-21 Chicago Union Rain C'!$A$1:$F$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2026-06-24 Ridgeville Parks'!$A$1:$F$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'2026-09-12 Block Party'!$A$1:$F$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2026-10-03 PTA'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2026-10-03 PTA'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="206">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -651,6 +651,55 @@
   </si>
   <si>
     <t>2026-10-03 | PTA</t>
+  </si>
+  <si>
+    <t>Drew sings "Time Flies", wait 4 beats then Jim starts drums for JLH</t>
+  </si>
+  <si>
+    <t>End on D, introduce band while Jack changes to acoustic guitar</t>
+  </si>
+  <si>
+    <t>Wrap up, end on A chord and let it ring out while Matt changes patch. When we finally stop, Matt will go right into PPC</t>
+  </si>
+  <si>
+    <t>End song as normal, once everything cuts out, Drew will start guitar riff for Seeker</t>
+  </si>
+  <si>
+    <t>End song as normal, let final A ring out for 4 beats then cut out as Jim starts drums for EotW</t>
+  </si>
+  <si>
+    <t>End on G and let ring out, once out Drew will start intro to FoAY</t>
+  </si>
+  <si>
+    <t>End song as normal, banter with the crowd while Jack switches to acoustic</t>
+  </si>
+  <si>
+    <t>End as normal, further banter while Miles and Jack switch instruments</t>
+  </si>
+  <si>
+    <t>End song as normal, then after a bit Drew will start guitar bit to lead into FIS</t>
+  </si>
+  <si>
+    <t>End song as normal, then Jim goes right into SO start</t>
+  </si>
+  <si>
+    <t>End song as normal, banter with crowd as Jim starts drum beat for BLY</t>
+  </si>
+  <si>
+    <t>BLY ends on B. Hit last B chord and wait four beats, then Jack will start right into Starlight (also on a B)</t>
+  </si>
+  <si>
+    <t>End song as normal and let ring out, as instruments are fading, Jim starts beat for NOtDO</t>
+  </si>
+  <si>
+    <t>End as normal, thank crowd, ask for follow and play last song</t>
+  </si>
+  <si>
+    <t>Transition Note for Next Song</t>
+  </si>
+  <si>
+    <t>2026-10-03
+PTA</t>
   </si>
 </sst>
 </file>
@@ -862,7 +911,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="87">
+  <borders count="84">
     <border>
       <left/>
       <right/>
@@ -1781,17 +1830,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1800,36 +1838,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1848,34 +1856,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -1936,33 +1920,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1984,12 +1942,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2362,35 +2374,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2436,42 +2441,50 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="19" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="19" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2848,7 +2861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD50"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" bestFit="1" customWidth="1"/>
@@ -2874,10 +2887,10 @@
     <col min="25" max="25" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="27" max="29" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" customWidth="1"/>
+    <col min="30" max="31" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="129" customFormat="1" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" s="129" customFormat="1" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2910,8 +2923,9 @@
       <c r="AB1" s="127"/>
       <c r="AC1" s="127"/>
       <c r="AD1" s="127"/>
-    </row>
-    <row r="2" spans="1:30" s="135" customFormat="1" ht="56" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE1" s="127"/>
+    </row>
+    <row r="2" spans="1:31" s="135" customFormat="1" ht="56" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="130" t="s">
         <v>1</v>
       </c>
@@ -3002,8 +3016,11 @@
       <c r="AD2" s="134" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:30" s="125" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE2" s="134" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" s="125" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="114" t="s">
         <v>31</v>
       </c>
@@ -3030,7 +3047,7 @@
         <v>36</v>
       </c>
       <c r="L3" s="136">
-        <f t="shared" ref="L3:L50" si="0">COUNTIF(M3:AD3,"✓")</f>
+        <f>COUNTIF(M3:AE3,"✓")</f>
         <v>0</v>
       </c>
       <c r="M3" s="117"/>
@@ -3051,15 +3068,19 @@
       <c r="AB3" s="114"/>
       <c r="AC3" s="114"/>
       <c r="AD3" s="114"/>
-    </row>
-    <row r="4" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE3" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A3)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="141" t="s">
+      <c r="B4" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="121" t="s">
@@ -3083,7 +3104,7 @@
       </c>
       <c r="K4" s="121"/>
       <c r="L4" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M4:AE4,"✓")</f>
         <v>2</v>
       </c>
       <c r="M4" s="123"/>
@@ -3108,15 +3129,19 @@
       <c r="AB4" s="121"/>
       <c r="AC4" s="121"/>
       <c r="AD4" s="121"/>
-    </row>
-    <row r="5" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE4" s="121" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A4)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="141" t="s">
+      <c r="B5" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="114" t="s">
@@ -3138,7 +3163,7 @@
       </c>
       <c r="K5" s="114"/>
       <c r="L5" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M5:AE5,"✓")</f>
         <v>3</v>
       </c>
       <c r="M5" s="117"/>
@@ -3165,15 +3190,19 @@
       <c r="AB5" s="114"/>
       <c r="AC5" s="114"/>
       <c r="AD5" s="114"/>
-    </row>
-    <row r="6" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE5" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A5)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="141" t="s">
+      <c r="B6" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="109" t="s">
@@ -3197,8 +3226,8 @@
       </c>
       <c r="K6" s="109"/>
       <c r="L6" s="136">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>COUNTIF(M6:AE6,"✓")</f>
+        <v>11</v>
       </c>
       <c r="M6" s="111"/>
       <c r="N6" s="111"/>
@@ -3238,15 +3267,19 @@
       <c r="AD6" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE6" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A6)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="141" t="s">
+      <c r="B7" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="114" t="s">
@@ -3270,7 +3303,7 @@
       </c>
       <c r="K7" s="114"/>
       <c r="L7" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M7:AE7,"✓")</f>
         <v>5</v>
       </c>
       <c r="M7" s="117"/>
@@ -3301,15 +3334,19 @@
       <c r="AD7" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE7" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A7)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="141" t="s">
+      <c r="B8" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="109" t="s">
@@ -3333,7 +3370,7 @@
       </c>
       <c r="K8" s="109"/>
       <c r="L8" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M8:AE8,"✓")</f>
         <v>5</v>
       </c>
       <c r="M8" s="111"/>
@@ -3364,15 +3401,19 @@
         <v>36</v>
       </c>
       <c r="AD8" s="109"/>
-    </row>
-    <row r="9" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE8" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A8)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="141" t="s">
+      <c r="B9" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="114" t="s">
@@ -3398,7 +3439,7 @@
       </c>
       <c r="K9" s="114"/>
       <c r="L9" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M9:AE9,"✓")</f>
         <v>9</v>
       </c>
       <c r="M9" s="117" t="s">
@@ -3437,15 +3478,19 @@
       <c r="AB9" s="114"/>
       <c r="AC9" s="114"/>
       <c r="AD9" s="114"/>
-    </row>
-    <row r="10" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE9" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A9)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="141" t="s">
+      <c r="B10" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="109" t="s">
@@ -3469,7 +3514,7 @@
       </c>
       <c r="K10" s="109"/>
       <c r="L10" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M10:AE10,"✓")</f>
         <v>18</v>
       </c>
       <c r="M10" s="111" t="s">
@@ -3526,15 +3571,19 @@
       <c r="AD10" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE10" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A10)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="141" t="s">
+      <c r="B11" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="114" t="s">
@@ -3558,7 +3607,7 @@
       </c>
       <c r="K11" s="114"/>
       <c r="L11" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M11:AE11,"✓")</f>
         <v>1</v>
       </c>
       <c r="M11" s="117"/>
@@ -3581,15 +3630,19 @@
       <c r="AB11" s="114"/>
       <c r="AC11" s="114"/>
       <c r="AD11" s="114"/>
-    </row>
-    <row r="12" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE11" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A11)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="141" t="s">
+      <c r="B12" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="109" t="s">
@@ -3611,7 +3664,7 @@
       </c>
       <c r="K12" s="109"/>
       <c r="L12" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M12:AE12,"✓")</f>
         <v>9</v>
       </c>
       <c r="M12" s="111" t="s">
@@ -3650,15 +3703,19 @@
       <c r="AB12" s="109"/>
       <c r="AC12" s="109"/>
       <c r="AD12" s="109"/>
-    </row>
-    <row r="13" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE12" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A12)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="141" t="s">
+      <c r="B13" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="114" t="s">
@@ -3682,8 +3739,8 @@
       </c>
       <c r="K13" s="114"/>
       <c r="L13" s="136">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>COUNTIF(M13:AE13,"✓")</f>
+        <v>8</v>
       </c>
       <c r="M13" s="117"/>
       <c r="N13" s="117"/>
@@ -3717,15 +3774,19 @@
       <c r="AD13" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE13" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A13)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="141" t="s">
+      <c r="B14" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="109" t="s">
@@ -3749,7 +3810,7 @@
       </c>
       <c r="K14" s="109"/>
       <c r="L14" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M14:AE14,"✓")</f>
         <v>2</v>
       </c>
       <c r="M14" s="111"/>
@@ -3774,15 +3835,19 @@
       <c r="AB14" s="109"/>
       <c r="AC14" s="109"/>
       <c r="AD14" s="109"/>
-    </row>
-    <row r="15" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE14" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A14)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="141" t="s">
+      <c r="B15" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="114" t="s">
@@ -3804,7 +3869,7 @@
       </c>
       <c r="K15" s="114"/>
       <c r="L15" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M15:AE15,"✓")</f>
         <v>1</v>
       </c>
       <c r="M15" s="117" t="s">
@@ -3827,15 +3892,19 @@
       <c r="AB15" s="114"/>
       <c r="AC15" s="114"/>
       <c r="AD15" s="114"/>
-    </row>
-    <row r="16" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE15" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A15)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="141" t="s">
+      <c r="B16" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="109" t="s">
@@ -3859,7 +3928,7 @@
       </c>
       <c r="K16" s="109"/>
       <c r="L16" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M16:AE16,"✓")</f>
         <v>13</v>
       </c>
       <c r="M16" s="111"/>
@@ -3906,15 +3975,19 @@
         <v>36</v>
       </c>
       <c r="AD16" s="109"/>
-    </row>
-    <row r="17" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE16" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A16)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="141" t="s">
+      <c r="B17" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="114" t="s">
@@ -3938,8 +4011,8 @@
       </c>
       <c r="K17" s="114"/>
       <c r="L17" s="136">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>COUNTIF(M17:AE17,"✓")</f>
+        <v>10</v>
       </c>
       <c r="M17" s="117" t="s">
         <v>36</v>
@@ -3977,15 +4050,19 @@
       <c r="AD17" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE17" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A17)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="141" t="s">
+      <c r="B18" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="109" t="s">
@@ -4009,8 +4086,8 @@
       </c>
       <c r="K18" s="109"/>
       <c r="L18" s="136">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTIF(M18:AE18,"✓")</f>
+        <v>2</v>
       </c>
       <c r="M18" s="111"/>
       <c r="N18" s="111"/>
@@ -4032,15 +4109,19 @@
       <c r="AB18" s="109"/>
       <c r="AC18" s="109"/>
       <c r="AD18" s="109"/>
-    </row>
-    <row r="19" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE18" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A18)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="141" t="s">
+      <c r="B19" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="114" t="s">
@@ -4064,8 +4145,8 @@
       </c>
       <c r="K19" s="114"/>
       <c r="L19" s="136">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>COUNTIF(M19:AE19,"✓")</f>
+        <v>9</v>
       </c>
       <c r="M19" s="117"/>
       <c r="N19" s="117"/>
@@ -4101,15 +4182,19 @@
         <v>36</v>
       </c>
       <c r="AD19" s="114"/>
-    </row>
-    <row r="20" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE19" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A19)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="141" t="s">
+      <c r="B20" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="109" t="s">
@@ -4133,8 +4218,8 @@
       </c>
       <c r="K20" s="109"/>
       <c r="L20" s="136">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>COUNTIF(M20:AE20,"✓")</f>
+        <v>7</v>
       </c>
       <c r="M20" s="111"/>
       <c r="N20" s="111"/>
@@ -4166,15 +4251,19 @@
       <c r="AD20" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE20" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A20)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="141" t="s">
+      <c r="B21" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="114" t="s">
@@ -4198,7 +4287,7 @@
       </c>
       <c r="K21" s="114"/>
       <c r="L21" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M21:AE21,"✓")</f>
         <v>9</v>
       </c>
       <c r="M21" s="117" t="s">
@@ -4237,15 +4326,19 @@
         <v>36</v>
       </c>
       <c r="AD21" s="114"/>
-    </row>
-    <row r="22" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE21" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A21)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="141" t="s">
+      <c r="B22" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="109" t="s">
@@ -4267,7 +4360,7 @@
       </c>
       <c r="K22" s="109"/>
       <c r="L22" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M22:AE22,"✓")</f>
         <v>1</v>
       </c>
       <c r="M22" s="111"/>
@@ -4290,15 +4383,19 @@
       <c r="AB22" s="109"/>
       <c r="AC22" s="109"/>
       <c r="AD22" s="109"/>
-    </row>
-    <row r="23" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE22" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A22)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="141" t="s">
+      <c r="B23" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="114" t="s">
@@ -4322,8 +4419,8 @@
       </c>
       <c r="K23" s="114"/>
       <c r="L23" s="136">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <f>COUNTIF(M23:AE23,"✓")</f>
+        <v>18</v>
       </c>
       <c r="M23" s="117" t="s">
         <v>36</v>
@@ -4377,15 +4474,19 @@
       <c r="AD23" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE23" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A23)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="141" t="s">
+      <c r="B24" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="109" t="s">
@@ -4409,7 +4510,7 @@
       </c>
       <c r="K24" s="109"/>
       <c r="L24" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M24:AE24,"✓")</f>
         <v>8</v>
       </c>
       <c r="M24" s="111"/>
@@ -4446,12 +4547,16 @@
       <c r="AB24" s="109"/>
       <c r="AC24" s="109"/>
       <c r="AD24" s="109"/>
-    </row>
-    <row r="25" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE24" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A24)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="141" t="s">
+      <c r="B25" s="138" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="119"/>
@@ -4476,7 +4581,7 @@
       </c>
       <c r="K25" s="114"/>
       <c r="L25" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M25:AE25,"✓")</f>
         <v>8</v>
       </c>
       <c r="M25" s="117"/>
@@ -4513,15 +4618,19 @@
       </c>
       <c r="AC25" s="114"/>
       <c r="AD25" s="114"/>
-    </row>
-    <row r="26" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE25" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A25)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="141" t="s">
+      <c r="B26" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="109" t="s">
@@ -4547,8 +4656,8 @@
       </c>
       <c r="K26" s="109"/>
       <c r="L26" s="136">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>COUNTIF(M26:AE26,"✓")</f>
+        <v>12</v>
       </c>
       <c r="M26" s="111"/>
       <c r="N26" s="111"/>
@@ -4590,15 +4699,19 @@
       <c r="AD26" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE26" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A26)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="114" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="141" t="s">
+      <c r="B27" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="114" t="s">
@@ -4622,7 +4735,7 @@
       </c>
       <c r="K27" s="114"/>
       <c r="L27" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M27:AE27,"✓")</f>
         <v>2</v>
       </c>
       <c r="M27" s="117"/>
@@ -4647,15 +4760,19 @@
       <c r="AD27" s="118" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE27" s="118" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A27)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="141" t="s">
+      <c r="B28" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="109" t="s">
@@ -4681,8 +4798,8 @@
       </c>
       <c r="K28" s="109"/>
       <c r="L28" s="136">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>COUNTIF(M28:AE28,"✓")</f>
+        <v>4</v>
       </c>
       <c r="M28" s="111"/>
       <c r="N28" s="111"/>
@@ -4708,15 +4825,19 @@
       <c r="AD28" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE28" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A28)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="141" t="s">
+      <c r="B29" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="114" t="s">
@@ -4740,7 +4861,7 @@
       </c>
       <c r="K29" s="114"/>
       <c r="L29" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M29:AE29,"✓")</f>
         <v>6</v>
       </c>
       <c r="M29" s="117"/>
@@ -4773,15 +4894,19 @@
       <c r="AD29" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE29" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A29)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="109" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="141" t="s">
+      <c r="B30" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="109" t="s">
@@ -4805,7 +4930,7 @@
       </c>
       <c r="K30" s="109"/>
       <c r="L30" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M30:AE30,"✓")</f>
         <v>13</v>
       </c>
       <c r="M30" s="111"/>
@@ -4852,15 +4977,19 @@
       <c r="AD30" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE30" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A30)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="141" t="s">
+      <c r="B31" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="114" t="s">
@@ -4884,8 +5013,8 @@
       </c>
       <c r="K31" s="114"/>
       <c r="L31" s="136">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>COUNTIF(M31:AE31,"✓")</f>
+        <v>17</v>
       </c>
       <c r="M31" s="117"/>
       <c r="N31" s="117"/>
@@ -4937,15 +5066,19 @@
       <c r="AD31" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE31" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A31)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="109" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="141" t="s">
+      <c r="B32" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="109" t="s">
@@ -4969,7 +5102,7 @@
       </c>
       <c r="K32" s="109"/>
       <c r="L32" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M32:AE32,"✓")</f>
         <v>2</v>
       </c>
       <c r="M32" s="111" t="s">
@@ -4994,15 +5127,19 @@
       <c r="AB32" s="109"/>
       <c r="AC32" s="109"/>
       <c r="AD32" s="109"/>
-    </row>
-    <row r="33" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE32" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A32)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="114" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="141" t="s">
+      <c r="B33" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="114" t="s">
@@ -5026,7 +5163,7 @@
       </c>
       <c r="K33" s="114"/>
       <c r="L33" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M33:AE33,"✓")</f>
         <v>7</v>
       </c>
       <c r="M33" s="117"/>
@@ -5061,15 +5198,19 @@
         <v>36</v>
       </c>
       <c r="AD33" s="114"/>
-    </row>
-    <row r="34" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE33" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A33)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="109" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="141" t="s">
+      <c r="B34" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="109" t="s">
@@ -5093,8 +5234,8 @@
       </c>
       <c r="K34" s="109"/>
       <c r="L34" s="136">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>COUNTIF(M34:AE34,"✓")</f>
+        <v>14</v>
       </c>
       <c r="M34" s="111"/>
       <c r="N34" s="111"/>
@@ -5140,15 +5281,19 @@
       <c r="AD34" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE34" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A34)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="141" t="s">
+      <c r="B35" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="114" t="s">
@@ -5170,7 +5315,7 @@
       </c>
       <c r="K35" s="114"/>
       <c r="L35" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M35:AE35,"✓")</f>
         <v>8</v>
       </c>
       <c r="M35" s="117"/>
@@ -5207,15 +5352,19 @@
       <c r="AB35" s="114"/>
       <c r="AC35" s="114"/>
       <c r="AD35" s="114"/>
-    </row>
-    <row r="36" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE35" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A35)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="B36" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="141" t="s">
+      <c r="B36" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="109" t="s">
@@ -5239,7 +5388,7 @@
       </c>
       <c r="K36" s="109"/>
       <c r="L36" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M36:AE36,"✓")</f>
         <v>9</v>
       </c>
       <c r="M36" s="111"/>
@@ -5278,15 +5427,19 @@
         <v>36</v>
       </c>
       <c r="AD36" s="109"/>
-    </row>
-    <row r="37" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE36" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A36)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="141" t="s">
+      <c r="B37" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="114" t="s">
@@ -5308,7 +5461,7 @@
       </c>
       <c r="K37" s="114"/>
       <c r="L37" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M37:AE37,"✓")</f>
         <v>4</v>
       </c>
       <c r="M37" s="117"/>
@@ -5337,15 +5490,19 @@
       <c r="AB37" s="114"/>
       <c r="AC37" s="114"/>
       <c r="AD37" s="114"/>
-    </row>
-    <row r="38" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE37" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A37)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="141" t="s">
+      <c r="B38" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="109" t="s">
@@ -5369,8 +5526,8 @@
       </c>
       <c r="K38" s="109"/>
       <c r="L38" s="136">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>COUNTIF(M38:AE38,"✓")</f>
+        <v>11</v>
       </c>
       <c r="M38" s="111"/>
       <c r="N38" s="111"/>
@@ -5410,15 +5567,19 @@
       <c r="AD38" s="109" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE38" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A38)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="141" t="s">
+      <c r="B39" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="114" t="s">
@@ -5442,8 +5603,8 @@
       </c>
       <c r="K39" s="114"/>
       <c r="L39" s="136">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>COUNTIF(M39:AE39,"✓")</f>
+        <v>7</v>
       </c>
       <c r="M39" s="117"/>
       <c r="N39" s="117"/>
@@ -5475,15 +5636,19 @@
       <c r="AD39" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE39" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A39)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="141" t="s">
+      <c r="B40" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="109" t="s">
@@ -5505,7 +5670,7 @@
       </c>
       <c r="K40" s="109"/>
       <c r="L40" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M40:AE40,"✓")</f>
         <v>2</v>
       </c>
       <c r="M40" s="111"/>
@@ -5530,15 +5695,19 @@
       <c r="AB40" s="109"/>
       <c r="AC40" s="109"/>
       <c r="AD40" s="109"/>
-    </row>
-    <row r="41" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE40" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A40)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="114" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="141" t="s">
+      <c r="B41" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="114" t="s">
@@ -5560,7 +5729,7 @@
       </c>
       <c r="K41" s="114"/>
       <c r="L41" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M41:AE41,"✓")</f>
         <v>1</v>
       </c>
       <c r="M41" s="117"/>
@@ -5583,15 +5752,19 @@
       <c r="AB41" s="114"/>
       <c r="AC41" s="114"/>
       <c r="AD41" s="114"/>
-    </row>
-    <row r="42" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE41" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A41)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="141" t="s">
+      <c r="B42" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="109" t="s">
@@ -5615,7 +5788,7 @@
       </c>
       <c r="K42" s="109"/>
       <c r="L42" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M42:AE42,"✓")</f>
         <v>3</v>
       </c>
       <c r="M42" s="111"/>
@@ -5642,15 +5815,19 @@
       <c r="AB42" s="109"/>
       <c r="AC42" s="109"/>
       <c r="AD42" s="109"/>
-    </row>
-    <row r="43" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE42" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A42)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="141" t="s">
+      <c r="B43" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="114" t="s">
@@ -5674,8 +5851,8 @@
       </c>
       <c r="K43" s="114"/>
       <c r="L43" s="136">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>COUNTIF(M43:AE43,"✓")</f>
+        <v>8</v>
       </c>
       <c r="M43" s="117"/>
       <c r="N43" s="117"/>
@@ -5709,15 +5886,19 @@
       <c r="AD43" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="44" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE43" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A43)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="141" t="s">
+      <c r="B44" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="109" t="s">
@@ -5739,7 +5920,7 @@
       </c>
       <c r="K44" s="109"/>
       <c r="L44" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M44:AE44,"✓")</f>
         <v>2</v>
       </c>
       <c r="M44" s="111"/>
@@ -5764,15 +5945,19 @@
       <c r="AB44" s="109"/>
       <c r="AC44" s="109"/>
       <c r="AD44" s="109"/>
-    </row>
-    <row r="45" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE44" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A44)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="114" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="141" t="s">
+      <c r="B45" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="114" t="s">
@@ -5796,7 +5981,7 @@
       </c>
       <c r="K45" s="114"/>
       <c r="L45" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M45:AE45,"✓")</f>
         <v>6</v>
       </c>
       <c r="M45" s="117"/>
@@ -5829,15 +6014,19 @@
       <c r="AD45" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="46" spans="1:30" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE45" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A45)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:31" s="113" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="141" t="s">
+      <c r="B46" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="109" t="s">
@@ -5861,7 +6050,7 @@
         <v>36</v>
       </c>
       <c r="L46" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M46:AE46,"✓")</f>
         <v>0</v>
       </c>
       <c r="M46" s="111"/>
@@ -5882,15 +6071,19 @@
       <c r="AB46" s="109"/>
       <c r="AC46" s="109"/>
       <c r="AD46" s="109"/>
-    </row>
-    <row r="47" spans="1:30" s="113" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE46" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A46)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:31" s="113" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="B47" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="141" t="s">
+      <c r="B47" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="114" t="s">
@@ -5914,8 +6107,8 @@
       </c>
       <c r="K47" s="114"/>
       <c r="L47" s="136">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>COUNTIF(M47:AE47,"✓")</f>
+        <v>19</v>
       </c>
       <c r="M47" s="117" t="s">
         <v>36</v>
@@ -5971,8 +6164,12 @@
       <c r="AD47" s="114" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="48" spans="1:30" s="113" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE47" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A47)&gt;0,"✓","")</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" s="113" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="109" t="s">
         <v>130</v>
       </c>
@@ -5995,7 +6192,7 @@
       </c>
       <c r="K48" s="109"/>
       <c r="L48" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M48:AE48,"✓")</f>
         <v>1</v>
       </c>
       <c r="M48" s="111"/>
@@ -6018,15 +6215,19 @@
       <c r="AB48" s="109"/>
       <c r="AC48" s="109"/>
       <c r="AD48" s="109"/>
-    </row>
-    <row r="49" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE48" s="109" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A48)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="114" t="s">
         <v>133</v>
       </c>
-      <c r="B49" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="141" t="s">
+      <c r="B49" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="138" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="114" t="s">
@@ -6050,7 +6251,7 @@
       </c>
       <c r="K49" s="114"/>
       <c r="L49" s="136">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M49:AE49,"✓")</f>
         <v>11</v>
       </c>
       <c r="M49" s="117" t="s">
@@ -6093,8 +6294,12 @@
         <v>36</v>
       </c>
       <c r="AD49" s="114"/>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="114" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A49)&gt;0,"✓","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -6107,7 +6312,7 @@
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="137">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(M50:AE50,"✓")</f>
         <v>0</v>
       </c>
       <c r="M50" s="4"/>
@@ -6128,6 +6333,10 @@
       <c r="AB50" s="4"/>
       <c r="AC50" s="4"/>
       <c r="AD50" s="4"/>
+      <c r="AE50" s="4" t="str">
+        <f>IF(COUNTIF('2026-10-03 PTA'!$B$4:$B$18,$A50)&gt;0,"✓","")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6236,6 +6445,7 @@
     <hyperlink ref="C47" r:id="rId87" xr:uid="{7419B077-C41D-854F-918E-C57ECDC53558}"/>
     <hyperlink ref="B49" r:id="rId88" xr:uid="{8D4B2197-8C02-804F-BE43-C2A6F5342B8B}"/>
     <hyperlink ref="C49" r:id="rId89" xr:uid="{A6F0842C-5B5F-1D43-B2FA-1A6F2E39E6E6}"/>
+    <hyperlink ref="AE2" location="'2026-10-03 PTA'!A1" tooltip="Go to 2026-10-03 PTA setlist" display="2026-10-03_x000a_PTA" xr:uid="{EEB538EA-0305-0945-A695-D9C968F1B1BC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6255,24 +6465,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -6560,24 +6770,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -7144,7 +7354,7 @@
       <c r="B31" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="142" t="s">
+      <c r="C31" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="17" t="s">
@@ -7326,24 +7536,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -7699,24 +7909,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -7825,10 +8035,10 @@
       <c r="B8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="142" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="142" t="s">
+      <c r="C8" s="139" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="139" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="10" t="s">
@@ -7926,7 +8136,7 @@
       <c r="B13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="17" t="s">
@@ -8087,24 +8297,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -8274,10 +8484,10 @@
       <c r="B11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="142" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="142" t="s">
+      <c r="C11" s="139" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="139" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="10" t="s">
@@ -8456,7 +8666,7 @@
       <c r="B20" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="17" t="s">
@@ -8791,24 +9001,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -9079,7 +9289,7 @@
       <c r="B16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="17" t="s">
@@ -9316,24 +9526,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -9503,7 +9713,7 @@
       <c r="B11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="17" t="s">
@@ -9711,24 +9921,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -9916,7 +10126,7 @@
       <c r="B12" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="142" t="s">
+      <c r="C12" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="17" t="s">
@@ -10037,24 +10247,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -10365,7 +10575,7 @@
       <c r="B18" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="17" t="s">
@@ -10700,24 +10910,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -10987,7 +11197,7 @@
       <c r="B16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="17" t="s">
@@ -11432,24 +11642,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -11760,24 +11970,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -12195,24 +12405,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -12524,24 +12734,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
@@ -12692,7 +12902,7 @@
       <c r="B10" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="142" t="s">
+      <c r="C10" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="17" t="s">
@@ -12824,27 +13034,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="143" t="s">
+    <row r="1" spans="1:7" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="184" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="145"/>
-    </row>
-    <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="186"/>
+    </row>
+    <row r="2" spans="1:7" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="146" t="s">
         <v>189</v>
       </c>
@@ -12852,459 +13064,455 @@
       <c r="C2" s="147"/>
       <c r="D2" s="147"/>
       <c r="E2" s="147"/>
-      <c r="F2" s="148"/>
-    </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="138"/>
-      <c r="B3" s="139" t="s">
+      <c r="F2" s="147"/>
+      <c r="G2" s="178"/>
+    </row>
+    <row r="3" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="171"/>
+      <c r="B3" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="183" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="183" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="139" t="s">
+      <c r="C3" s="144" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="144" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="174" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="140" t="s">
+      <c r="F3" s="175" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+      <c r="G3" s="183" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
         <v>1</v>
       </c>
-      <c r="B4" s="179" t="s">
+      <c r="B4" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="181" t="s">
+      <c r="C4" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="24">
-        <v>2.60416666666667E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>2</v>
-      </c>
-      <c r="B5" s="179" t="s">
+      <c r="F4" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B4,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.604166666666667E-3</v>
+      </c>
+      <c r="G4" s="182" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A5" s="18">
+        <v>2</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="181" t="s">
+      <c r="C5" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="24">
-        <v>2.5810185185185198E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>3</v>
-      </c>
-      <c r="B6" s="179" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="181" t="s">
+      <c r="F5" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B5,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.5810185185185189E-3</v>
+      </c>
+      <c r="G5" s="179" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A6" s="18">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="143" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B6,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>3.0439814814814808E-3</v>
+      </c>
+      <c r="G6" s="179" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A7" s="18">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="143" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B7,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.9513888888888888E-3</v>
+      </c>
+      <c r="G7" s="179" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A8" s="18">
+        <v>5</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="143" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B8,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.2569444444444438E-3</v>
+      </c>
+      <c r="G8" s="179" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A9" s="18">
+        <v>6</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="143" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B9,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.743055555555555E-3</v>
+      </c>
+      <c r="G9" s="179" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A10" s="18">
+        <v>7</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="143" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B10,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.488425925925926E-3</v>
+      </c>
+      <c r="G10" s="179" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A11" s="18">
+        <v>8</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="143" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B11,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>1.9791666666666668E-3</v>
+      </c>
+      <c r="G11" s="179" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
+        <v>9</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="24">
-        <v>2.7893518518518502E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <v>4</v>
-      </c>
-      <c r="B7" s="179" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="181" t="s">
+      <c r="F12" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B12,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.430555555555556E-3</v>
+      </c>
+      <c r="G12" s="179" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A13" s="18">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="143" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B13,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>1.93287037037037E-3</v>
+      </c>
+      <c r="G13" s="179" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A14" s="18">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="24">
-        <v>2.2569444444444399E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
-        <v>5</v>
-      </c>
-      <c r="B8" s="179" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="181" t="s">
+      <c r="F14" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B14,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>3.368055555555556E-3</v>
+      </c>
+      <c r="G14" s="179" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A15" s="18">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="24">
-        <v>2.7430555555555602E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
-        <v>6</v>
-      </c>
-      <c r="B9" s="179" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="181" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="24">
-        <v>1.9791666666666699E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
-        <v>7</v>
-      </c>
-      <c r="B10" s="179" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="181" t="s">
+      <c r="F15" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B15,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.5810185185185189E-3</v>
+      </c>
+      <c r="G15" s="179" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A16" s="18">
+        <v>13</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="24">
-        <v>2.04861111111111E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
-        <v>8</v>
-      </c>
-      <c r="B11" s="179" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="181" t="s">
+      <c r="F16" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B16,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>2.604166666666667E-3</v>
+      </c>
+      <c r="G16" s="179" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="A17" s="18">
+        <v>14</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="24">
-        <v>2.9513888888888901E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
-        <v>9</v>
-      </c>
-      <c r="B12" s="179" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="24">
-        <v>2.4305555555555599E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
-        <v>10</v>
-      </c>
-      <c r="B13" s="179" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="181" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="24">
-        <v>2.71990740740741E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
-        <v>11</v>
-      </c>
-      <c r="B14" s="179" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="24">
-        <v>2.6504629629629599E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <v>12</v>
-      </c>
-      <c r="B15" s="179" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="181" t="s">
+      <c r="F17" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B17,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>3.5995370370370369E-3</v>
+      </c>
+      <c r="G17" s="179" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="24">
-        <v>2.60416666666667E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
-        <v>13</v>
-      </c>
-      <c r="B16" s="179" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="178" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="178" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="181" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="24">
-        <f>'Song Tracker'!F28</f>
-        <v>3.0439814814814808E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
-        <v>14</v>
-      </c>
-      <c r="B17" s="179" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="24">
-        <v>2.0833333333333298E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
-        <v>15</v>
-      </c>
-      <c r="B18" s="179" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="181" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="24">
-        <v>2.8587962962962998E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
-        <v>16</v>
-      </c>
-      <c r="B19" s="179" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="181" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="24">
-        <v>3.59953703703704E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="172">
-        <v>17</v>
-      </c>
-      <c r="B20" s="180" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="182" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="173">
-        <v>3.2291666666666701E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
-        <v>18</v>
-      </c>
-      <c r="B21" s="179" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="181" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="24">
-        <v>3.32175925925926E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="174"/>
-      <c r="B22" s="175" t="s">
+      <c r="F18" s="176">
+        <f>INDEX('Song Tracker'!$F$3:$F$50,MATCH($B18,'Song Tracker'!$A$3:$A$50,0))</f>
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="G18" s="180"/>
+    </row>
+    <row r="19" spans="1:7" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="140"/>
+      <c r="B19" s="141" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="185"/>
-      <c r="D22" s="185"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="177">
-        <f>SUM(F4:F21)</f>
-        <v>4.8495370370370397E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="177">
+        <f>SUM(F4:F18)</f>
+        <v>4.0486111111111112E-2</v>
+      </c>
+      <c r="G19" s="181"/>
+    </row>
+    <row r="20" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{0CD0CEF0-CEB2-A246-AC49-3CAC425C85B8}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{1E727846-5FB7-F942-B6E1-4061453D063E}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{DA3C922F-6C54-0142-BCD2-3F7B7760929C}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{C365DACB-9A78-6B41-90A7-FD4D2480B337}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{21930CF6-61E8-E948-A127-589B4EBC3368}"/>
-    <hyperlink ref="D6" r:id="rId6" xr:uid="{9DC59632-AF22-714F-BAC4-6C5E45CC6FAA}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{FA6A5E28-1CAF-5741-95AC-2CDB54CB7642}"/>
-    <hyperlink ref="D7" r:id="rId8" xr:uid="{521CCC89-A496-0C4D-95C2-C7B4743FAF4E}"/>
-    <hyperlink ref="C8" r:id="rId9" xr:uid="{641E1802-EA28-8741-95E4-905554D891C3}"/>
-    <hyperlink ref="D8" r:id="rId10" xr:uid="{429C7CDB-A616-1F4A-AC21-B6347D046CE0}"/>
-    <hyperlink ref="C9" r:id="rId11" xr:uid="{9C117EC0-FCCC-2740-A303-C09507421392}"/>
-    <hyperlink ref="D9" r:id="rId12" xr:uid="{F9096CAD-F0F2-B243-AAC1-F47C7BB02D28}"/>
-    <hyperlink ref="C10" r:id="rId13" xr:uid="{692E011F-2691-1044-B7C1-B91D93F17C66}"/>
-    <hyperlink ref="D10" r:id="rId14" xr:uid="{9D97B550-A21C-0B4C-96B5-409599034AED}"/>
-    <hyperlink ref="C11" r:id="rId15" xr:uid="{55EC590C-1B72-044C-8456-20423FBA8ADA}"/>
-    <hyperlink ref="D11" r:id="rId16" xr:uid="{95D59F58-1983-BA45-9968-C0927799F552}"/>
-    <hyperlink ref="C12" r:id="rId17" xr:uid="{33BF72F0-61F0-CF46-9933-47729DDC9702}"/>
-    <hyperlink ref="D12" r:id="rId18" xr:uid="{A74E614C-625C-CF45-A94C-82E326E2522A}"/>
-    <hyperlink ref="C13" r:id="rId19" xr:uid="{9ED99007-BC44-3441-8E74-C31250DA365F}"/>
-    <hyperlink ref="D13" r:id="rId20" xr:uid="{07C87020-817F-5040-806B-7660DC71AE85}"/>
-    <hyperlink ref="C14" r:id="rId21" xr:uid="{5F3E4947-3379-5D4B-8AD8-C7C8ABCD61B5}"/>
-    <hyperlink ref="D14" r:id="rId22" xr:uid="{B49DA0D5-0856-8B49-B6C2-FCB712E69D8B}"/>
-    <hyperlink ref="C15" r:id="rId23" xr:uid="{DC9AAF63-B84B-7C44-960A-D0230BACFA53}"/>
-    <hyperlink ref="D15" r:id="rId24" xr:uid="{E9440E9B-D597-E54A-A551-4C8A7FB43178}"/>
-    <hyperlink ref="C17" r:id="rId25" xr:uid="{B932668A-6A89-734A-B68D-28094B1BD55F}"/>
-    <hyperlink ref="D17" r:id="rId26" xr:uid="{09690B73-8AE0-D34B-A684-ADD2C83B26B8}"/>
-    <hyperlink ref="C18" r:id="rId27" xr:uid="{C8E54C2B-AF17-3248-8356-DE741DE479E9}"/>
-    <hyperlink ref="D18" r:id="rId28" xr:uid="{2BE56037-38B3-3B47-9865-C68641F54377}"/>
-    <hyperlink ref="C19" r:id="rId29" xr:uid="{3005EC63-4DA5-C34B-A198-6E5596B25088}"/>
-    <hyperlink ref="D19" r:id="rId30" xr:uid="{4FDBD01C-17A4-C94A-B53A-7281371DDA02}"/>
-    <hyperlink ref="C20" r:id="rId31" xr:uid="{B91EBDC5-ABC4-914D-B066-5F3F1A7A2AF8}"/>
-    <hyperlink ref="D20" r:id="rId32" xr:uid="{3FA66CC4-2C42-0C4D-869E-1C4EDECE3172}"/>
-    <hyperlink ref="C21" r:id="rId33" xr:uid="{82814134-668A-204E-A94A-41E70CCC41B7}"/>
-    <hyperlink ref="D21" r:id="rId34" xr:uid="{1F3E435F-9F35-0140-A080-6722111D443E}"/>
-    <hyperlink ref="C16" r:id="rId35" xr:uid="{82AC4A7B-646F-B949-81E6-4FC846671668}"/>
-    <hyperlink ref="D16" r:id="rId36" xr:uid="{8B381F23-5675-894E-ACE2-ACD58A2CD001}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{68BA07A1-62A1-2D42-B701-8F55605C180F}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{1E16E4CD-2AC6-BA4E-A462-99D6D8126EF1}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{62DA795D-B8E7-D54A-BD9A-08E02F4A465B}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{CC693FBA-C6E8-3B4C-B4B5-D0E3AFED2FF4}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{6FA9BDB4-F910-FA4D-A38F-9EC25B7BC0A4}"/>
+    <hyperlink ref="D6" r:id="rId6" xr:uid="{42F697D5-669C-5A46-A88A-C3001C6283E4}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{90F30723-D06A-E846-B04F-6FC8C5BA2384}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{265ED2BF-D67A-AB4E-B54B-A3D32B1EC385}"/>
+    <hyperlink ref="C8" r:id="rId9" xr:uid="{CCD796BB-56E6-EC4B-8D25-2677292ACE53}"/>
+    <hyperlink ref="D8" r:id="rId10" xr:uid="{DF6BE37A-793E-A944-8F52-5435D99A9571}"/>
+    <hyperlink ref="C9" r:id="rId11" xr:uid="{C1AC7F24-8F7B-3549-97EB-A5F033E03F9F}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{8B8974C3-B170-4540-A02F-3AB217EC9A9F}"/>
+    <hyperlink ref="C10" r:id="rId13" xr:uid="{84086B92-3B86-3E40-962C-0A0C88C2400B}"/>
+    <hyperlink ref="D10" r:id="rId14" xr:uid="{7F61DCC1-E224-AF48-ABFA-576BEC571315}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{AFC0652F-9AF4-CA47-AA35-C8D99DADCD1E}"/>
+    <hyperlink ref="D11" r:id="rId16" xr:uid="{FB0F7747-7039-8C40-9918-B50CD7E7BB20}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{ADDC74F2-B4BE-D148-B907-ADB147A81B8B}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{16A821E5-4A0D-4B44-9DA6-4115E08DEAD7}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{A15C9D6F-03CA-4A4B-B75E-8E233978CB7A}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{18EC77FE-C942-0648-836C-4ED7E156A06E}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{8D756A0E-B3BE-5D4B-81BB-356CD6A5277B}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{57D22F25-7DD0-554C-8C67-561914C9302E}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{7F405978-DD23-454F-A25E-CAC5A2834FE5}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{EA54F49B-D91B-134E-AD1D-81D0E1752B0C}"/>
+    <hyperlink ref="C16" r:id="rId25" xr:uid="{1C2FA8A3-958C-0F48-B44C-F83846EAF240}"/>
+    <hyperlink ref="D16" r:id="rId26" xr:uid="{E3AFE58E-EA2F-4F43-9BB6-50C42C85A313}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{1E724492-79AB-A44F-8AC9-8D39AAF4BA0B}"/>
+    <hyperlink ref="D17" r:id="rId28" xr:uid="{B583FF1C-B229-8D4F-8056-7C9C94F09E00}"/>
+    <hyperlink ref="C18" r:id="rId29" xr:uid="{5DC31820-F4BD-794D-87C4-DEE74C90E230}"/>
+    <hyperlink ref="D18" r:id="rId30" xr:uid="{2F80196E-EAE5-2343-A995-6E0A90807BA5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="79" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13324,24 +13532,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="82" t="s">
@@ -13827,24 +14035,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="82" t="s">
@@ -14147,14 +14355,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="153" t="s">
+      <c r="A18" s="152" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="154"/>
-      <c r="C18" s="154"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="155"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="154"/>
     </row>
     <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="93">
@@ -14495,24 +14703,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="158" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="161"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="160"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="155" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="158"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="157"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
@@ -14851,12 +15059,12 @@
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="61"/>
-      <c r="B19" s="162" t="s">
+      <c r="B19" s="161" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="160"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="160"/>
+      <c r="C19" s="159"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
       <c r="F19" s="75">
         <f>SUM(F4:F18)</f>
         <v>4.0509259259259259E-2</v>
@@ -14918,14 +15126,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="162" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="164"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="163"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
@@ -15228,14 +15436,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="165" t="s">
+      <c r="A17" s="164" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="155"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="154"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="43">
@@ -15575,24 +15783,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="168" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="171"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="170"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="165" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="167"/>
-      <c r="C2" s="167"/>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
-      <c r="F2" s="168"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="167"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="86" t="s">
@@ -16010,24 +16218,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
